--- a/04_DESIGN_TABLES/DesignTable_6501.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6501.xlsx
@@ -1765,24 +1765,61 @@
           <t>6501-06-06-FG</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>3/8</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>6501-06-06-FG</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 9/16-18 (B UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-06-06 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): N@DRIVE: OMi Items row 1944 L 1 Size = 1.220; M5@DRIVE: OMi Items row 1944 M 2 Size = 1.280; M10@DRIVE: OMi Items row 1944 M 1 Size = 0.910; C3HEX@HEX: OMi Items row 1944 Nut Hex 1 = 0.688; Y@HEX: OMi Items row 1944 Hex Flat = 0.750; D1@BORE: OMi Items row 1944 Side 1 ID = 0.406; D@BORE: OMi Items row 1944 Side 2 ID = 0.297; THDMAJ_A@DRIVE: 3/8-18 -&gt; 0.675 (end library); THDMAJ_B@DRIVE: 9/16-18 -&gt; 0.5625 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male pipe leg (catalog N), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 ID = pipe-end bore, Side 2 ID = swivel bore (batch-15 pairing, Brennan TFA p35 letters)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1944 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p035-t01: TUBE O.D. 3/8, A NPTF 3/8-18, B SAE 37Deg 9/16-18, A DRILL 0.406, B DRILL 0.297, M4 LGTH 0.90, M6 LGTH 1.28, N LGTH 1.22, C HEX 0.688, Y FLATS 0.750</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2098,24 +2135,61 @@
           <t>6501-12-08-FG</t>
         </is>
       </c>
+      <c r="B26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>6501-12-08-FG</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF) x 3/4-16 (B UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING; 2026-10-09 (left out of batch 15, staged): N@DRIVE: OMi Items row 1949 L 1 Size = 1.590; M5@DRIVE: OMi Items row 1949 M 2 Size = 1.540; M10@DRIVE: OMi Items row 1949 M 1 Size = 1.120; C3HEX@HEX: OMi Items row 1949 Nut Hex 1 = 0.875; Y@HEX: OMi Items row 1949 Hex Flat = 1.062; D1@BORE: OMi Items row 1949 Side 1 ID = 0.719; D@BORE: OMi Items row 1949 Side 2 ID = 0.391; THDMAJ_A@DRIVE: 3/4-14 -&gt; 1.05 (end library); THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male pipe leg (catalog N), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 ID = pipe-end bore, Side 2 ID = swivel bore (batch-15 pairing, Brennan TFA p35 letters)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1949 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p035-t01: TUBE O.D. 3/4, A NPTF 3/4-14, B SAE 37Deg 3/4-16, A DRILL 0.719, B DRILL 0.391, M4 LGTH 1.120, M6 LGTH 1.612, N LGTH 1.590, C HEX 0.875, Y FLATS 1.062</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2135,24 +2209,61 @@
           <t>6501-12-12-FG</t>
         </is>
       </c>
+      <c r="B27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>6501-12-12-FG</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF) x 1 1/16-12 (B UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-12-12 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): N@DRIVE: OMi Items row 1950 L 1 Size = 1.590; M5@DRIVE: OMi Items row 1950 M 2 Size = 1.750; M10@DRIVE: OMi Items row 1950 M 1 Size = 1.190; C3HEX@HEX: OMi Items row 1950 Nut Hex 1 = 1.25; Y@HEX: OMi Items row 1950 Hex Flat = 1.063; D1@BORE: OMi Items row 1950 Side 1 ID = 0.719; D@BORE: OMi Items row 1950 Side 2 ID = 0.609; THDMAJ_A@DRIVE: 3/4-14 -&gt; 1.05 (end library); THDMAJ_B@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male pipe leg (catalog N), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 ID = pipe-end bore, Side 2 ID = swivel bore (batch-15 pairing, Brennan TFA p35 letters)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1950 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p035-t01: TUBE O.D. 3/4, A NPTF 3/4-14, B SAE 37Deg 1-1/16-12, A DRILL 0.719, B DRILL 0.609, M4 LGTH 1.180, M6 LGTH 1.750, N LGTH 1.590, C HEX 1.250, Y FLATS 1.062</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6501.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6501.xlsx
@@ -727,10 +727,10 @@
         <v>1.09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="D6" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
         <v>0.5600000000000001</v>
@@ -772,7 +772,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Air-Way s132 only (double-pass 16 rows)</t>
+          <t>Air-Way s132 only (double-pass 16 rows); M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1941 = 0.800 (table had 0.77) [user 2026-10-18 A19]; M5@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!O1941 = 1.140 (table had 1.11) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): M10@DRIVE 0.77 -&gt; OMi 0.800 (Items!N1941, M127) | A19 (user 2026-10-18, group 2 settled): M5@DRIVE 1.11 -&gt; OMi 1.140 (Items!O1941, M128)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6501.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6501.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -727,10 +727,10 @@
         <v>1.09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="E6" t="n">
         <v>0.5600000000000001</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Air-Way s132 only (double-pass 16 rows); M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1941 = 0.800 (table had 0.77) [user 2026-10-18 A19]; M5@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!O1941 = 1.140 (table had 1.11) [user 2026-10-18 A19]</t>
+          <t>Air-Way s132 only (double-pass 16 rows); M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1941 = 0.800 (table had 0.77) [user 2026-10-18 A19]; M5@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!O1941 = 1.140 (table had 1.11) [user 2026-10-18 A19]; M5@DRIVE: Air-Way 1.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; M10@DRIVE: Air-Way 0.77 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): M10@DRIVE 0.77 -&gt; OMi 0.800 (Items!N1941, M127) | A19 (user 2026-10-18, group 2 settled): M5@DRIVE 1.11 -&gt; OMi 1.140 (Items!O1941, M128)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): M10@DRIVE 0.77 -&gt; OMi 0.800 (Items!N1941, M127) | A19 (user 2026-10-18, group 2 settled): M5@DRIVE 1.11 -&gt; OMi 1.140 (Items!O1941, M128) | 2026-10-20 Air-Way first: M5@DRIVE OMi/Brennan 1.14 -&gt; Air-Way 1.11 | 2026-10-20 Air-Way first: M10@DRIVE OMi/Brennan 0.8 -&gt; Air-Way 0.77</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
